--- a/jadwal_master_imunisasi.xlsx
+++ b/jadwal_master_imunisasi.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A74940-122D-F645-96F4-BBB504316B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="-21000" windowWidth="19200" windowHeight="21000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="-21000" windowWidth="31440" windowHeight="19300" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
